--- a/artfynd/A 24597-2026 artfynd.xlsx
+++ b/artfynd/A 24597-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134056969</v>
       </c>
       <c r="B2" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134056755</v>
       </c>
       <c r="B3" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>134057029</v>
       </c>
       <c r="B4" t="n">
-        <v>58117</v>
+        <v>58124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>134057021</v>
       </c>
       <c r="B5" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24597-2026 artfynd.xlsx
+++ b/artfynd/A 24597-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134056969</v>
       </c>
       <c r="B2" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134056755</v>
       </c>
       <c r="B3" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>134057029</v>
       </c>
       <c r="B4" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>134057021</v>
       </c>
       <c r="B5" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24597-2026 artfynd.xlsx
+++ b/artfynd/A 24597-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134056969</v>
+        <v>134056755</v>
       </c>
       <c r="B2" t="n">
         <v>58260</v>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399597</v>
+        <v>399550</v>
       </c>
       <c r="R2" t="n">
-        <v>6207478</v>
+        <v>6207406</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,6 +772,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>källa vid alkärr</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134056755</v>
+        <v>134056969</v>
       </c>
       <c r="B3" t="n">
         <v>58260</v>
@@ -843,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399550</v>
+        <v>399597</v>
       </c>
       <c r="R3" t="n">
-        <v>6207406</v>
+        <v>6207478</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,16 +899,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Bäck</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>källa vid alkärr</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134057029</v>
+        <v>134057021</v>
       </c>
       <c r="B4" t="n">
-        <v>58134</v>
+        <v>58260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134057021</v>
+        <v>134057029</v>
       </c>
       <c r="B5" t="n">
-        <v>58260</v>
+        <v>58134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">

--- a/artfynd/A 24597-2026 artfynd.xlsx
+++ b/artfynd/A 24597-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134056755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134056969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134057021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,8 +1170,19 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134057029</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>